--- a/Data/National Accounts/PSA-04EOG_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-04EOG_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D144C65E-6B26-4C04-815D-1985D078FA3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DE33C3F-E045-408B-A836-B0693C61BE7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EOG" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="85">
   <si>
     <t>Source: Philippine Statistics Authority</t>
   </si>
@@ -294,9 +294,6 @@
     <t>2023 - 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
-  </si>
-  <si>
     <t>Annual 2000 to 2025</t>
   </si>
   <si>
@@ -307,6 +304,12 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>As of April 2026</t>
+  </si>
+  <si>
+    <t>Note: * means more than 1000%, - means zero</t>
   </si>
 </sst>
 </file>
@@ -441,15 +444,7 @@
     <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
     <cellStyle name="Normal 2 2" xfId="5" xr:uid="{DF2F7743-8CF8-4A35-94B9-0A3611B1D0EA}"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -761,7 +756,7 @@
     </row>
     <row r="3" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:96" x14ac:dyDescent="0.2">
@@ -771,7 +766,7 @@
     </row>
     <row r="6" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:96" x14ac:dyDescent="0.2">
@@ -973,10 +968,10 @@
         <v>2041600.7107911867</v>
       </c>
       <c r="Z12" s="8">
-        <v>1944552.8767487591</v>
+        <v>1944603.7719269143</v>
       </c>
       <c r="AA12" s="8">
-        <v>2382368.2282448704</v>
+        <v>2383821.9663259462</v>
       </c>
       <c r="AB12" s="9"/>
       <c r="AC12" s="9"/>
@@ -1125,10 +1120,10 @@
         <v>1540972.8377534701</v>
       </c>
       <c r="Z13" s="11">
-        <v>1318849.0595251855</v>
+        <v>1318851.6232509606</v>
       </c>
       <c r="AA13" s="11">
-        <v>1681118.0784127093</v>
+        <v>1682599.6935113948</v>
       </c>
       <c r="AB13" s="9"/>
       <c r="AC13" s="9"/>
@@ -1277,10 +1272,10 @@
         <v>142195.85522264367</v>
       </c>
       <c r="Z14" s="11">
-        <v>182803.32567623712</v>
+        <v>182815.04327678506</v>
       </c>
       <c r="AA14" s="11">
-        <v>212790.05967496487</v>
+        <v>205336.87244529929</v>
       </c>
       <c r="AB14" s="9"/>
       <c r="AC14" s="9"/>
@@ -1432,7 +1427,7 @@
         <v>47020.191825708127</v>
       </c>
       <c r="AA15" s="11">
-        <v>56662.54271138912</v>
+        <v>57137.410606841338</v>
       </c>
       <c r="AB15" s="9"/>
       <c r="AC15" s="9"/>
@@ -1578,13 +1573,13 @@
         <v>60394.649109861399</v>
       </c>
       <c r="Y16" s="11">
-        <v>62688.463617262583</v>
+        <v>62688.463617262605</v>
       </c>
       <c r="Z16" s="11">
-        <v>114724.86629014532</v>
+        <v>114729.35280349644</v>
       </c>
       <c r="AA16" s="11">
-        <v>122654.24044773469</v>
+        <v>123711.1822974736</v>
       </c>
       <c r="AB16" s="9"/>
       <c r="AC16" s="9"/>
@@ -1733,10 +1728,10 @@
         <v>44038.758392179945</v>
       </c>
       <c r="Z17" s="11">
-        <v>49952.389183510037</v>
+        <v>49979.907511775942</v>
       </c>
       <c r="AA17" s="11">
-        <v>58432.964088283159</v>
+        <v>57168.905632371359</v>
       </c>
       <c r="AB17" s="9"/>
       <c r="AC17" s="9"/>
@@ -1885,10 +1880,10 @@
         <v>34583.985699103723</v>
       </c>
       <c r="Z18" s="11">
-        <v>32971.351696649392</v>
+        <v>32971.897568435263</v>
       </c>
       <c r="AA18" s="11">
-        <v>16936.391659712004</v>
+        <v>27859.002345887842</v>
       </c>
       <c r="AB18" s="9"/>
       <c r="AC18" s="9"/>
@@ -2040,7 +2035,7 @@
         <v>181250.73830291582</v>
       </c>
       <c r="AA19" s="11">
-        <v>210065.19889387742</v>
+        <v>206312.82718794042</v>
       </c>
       <c r="AB19" s="9"/>
       <c r="AC19" s="9"/>
@@ -2189,10 +2184,10 @@
         <v>9653.2417108838836</v>
       </c>
       <c r="Z20" s="11">
-        <v>12862.573249469449</v>
+        <v>12866.636387898741</v>
       </c>
       <c r="AA20" s="11">
-        <v>18607.066106185732</v>
+        <v>18606.200275045245</v>
       </c>
       <c r="AB20" s="9"/>
       <c r="AC20" s="9"/>
@@ -2344,7 +2339,7 @@
         <v>4118.3809989382589</v>
       </c>
       <c r="AA21" s="11">
-        <v>5101.6862500144807</v>
+        <v>5089.8720236919207</v>
       </c>
       <c r="AB21" s="9"/>
       <c r="AC21" s="9"/>
@@ -2493,10 +2488,10 @@
         <v>235873.67196421762</v>
       </c>
       <c r="Z22" s="8">
-        <v>305778.72826115985</v>
+        <v>306337.47747658589</v>
       </c>
       <c r="AA22" s="8">
-        <v>379351.72309194587</v>
+        <v>382166.61759024143</v>
       </c>
       <c r="AB22" s="9"/>
       <c r="AC22" s="9"/>
@@ -2645,10 +2640,10 @@
         <v>62945.65414760822</v>
       </c>
       <c r="Z23" s="11">
-        <v>65025.851095708022</v>
+        <v>65002.220316552222</v>
       </c>
       <c r="AA23" s="11">
-        <v>89222.846194087659</v>
+        <v>89373.086991373741</v>
       </c>
       <c r="AB23" s="9"/>
       <c r="AC23" s="9"/>
@@ -2797,10 +2792,10 @@
         <v>59812.765426135447</v>
       </c>
       <c r="Z24" s="11">
-        <v>115209.08760863032</v>
+        <v>116924.7215475431</v>
       </c>
       <c r="AA24" s="11">
-        <v>145374.26221524464</v>
+        <v>147678.77050613638</v>
       </c>
       <c r="AB24" s="9"/>
       <c r="AC24" s="9"/>
@@ -2949,10 +2944,10 @@
         <v>3559.3236528613161</v>
       </c>
       <c r="Z25" s="11">
-        <v>2959.4268198494228</v>
+        <v>3159.0961756883394</v>
       </c>
       <c r="AA25" s="11">
-        <v>2526.8076835149714</v>
+        <v>3000.6668199143396</v>
       </c>
       <c r="AB25" s="9"/>
       <c r="AC25" s="9"/>
@@ -3101,10 +3096,10 @@
         <v>12255.710909945119</v>
       </c>
       <c r="Z26" s="11">
-        <v>15445.148944568187</v>
+        <v>15431.552855789589</v>
       </c>
       <c r="AA26" s="11">
-        <v>27443.325947342353</v>
+        <v>27517.611231759562</v>
       </c>
       <c r="AB26" s="9"/>
       <c r="AC26" s="9"/>
@@ -3253,10 +3248,10 @@
         <v>5162.9916103674586</v>
       </c>
       <c r="Z27" s="11">
-        <v>3673.6631274079264</v>
+        <v>3566.4681816586126</v>
       </c>
       <c r="AA27" s="11">
-        <v>3067.0093293516848</v>
+        <v>3005.7027510396147</v>
       </c>
       <c r="AB27" s="9"/>
       <c r="AC27" s="9"/>
@@ -3405,10 +3400,10 @@
         <v>37945.991995885866</v>
       </c>
       <c r="Z28" s="11">
-        <v>42111.870222360943</v>
+        <v>42110.050420164749</v>
       </c>
       <c r="AA28" s="11">
-        <v>48574.134652536035</v>
+        <v>48591.566371247158</v>
       </c>
       <c r="AB28" s="9"/>
       <c r="AC28" s="9"/>
@@ -3709,10 +3704,10 @@
         <v>54191.135184677856</v>
       </c>
       <c r="Z30" s="11">
-        <v>61353.065991662639</v>
+        <v>60142.753528216854</v>
       </c>
       <c r="AA30" s="11">
-        <v>63143.337069868488</v>
+        <v>62999.21291877066</v>
       </c>
       <c r="AB30" s="9"/>
       <c r="AC30" s="9"/>
@@ -3861,10 +3856,10 @@
         <v>33272.307105464031</v>
       </c>
       <c r="Z31" s="8">
-        <v>38825.456081327298</v>
+        <v>38624.219651579391</v>
       </c>
       <c r="AA31" s="8">
-        <v>35768.530057399956</v>
+        <v>35779.930426905899</v>
       </c>
       <c r="AB31" s="9"/>
       <c r="AC31" s="9"/>
@@ -4013,10 +4008,10 @@
         <v>14837.937077723247</v>
       </c>
       <c r="Z32" s="11">
-        <v>15190.686833784688</v>
+        <v>14942.097712890996</v>
       </c>
       <c r="AA32" s="11">
-        <v>15017.767842552486</v>
+        <v>15012.389142045968</v>
       </c>
       <c r="AB32" s="9"/>
       <c r="AC32" s="9"/>
@@ -4165,10 +4160,10 @@
         <v>18434.370027740784</v>
       </c>
       <c r="Z33" s="11">
-        <v>23634.769247542608</v>
+        <v>23682.121938688397</v>
       </c>
       <c r="AA33" s="11">
-        <v>20750.762214847469</v>
+        <v>20767.54128485993</v>
       </c>
       <c r="AB33" s="9"/>
       <c r="AC33" s="9"/>
@@ -4317,10 +4312,10 @@
         <v>37643.408283962592</v>
       </c>
       <c r="Z34" s="11">
-        <v>35958.198180127278</v>
+        <v>36013.536765832425</v>
       </c>
       <c r="AA34" s="11">
-        <v>38067.370044583149</v>
+        <v>38120.047769643228</v>
       </c>
       <c r="AB34" s="9"/>
       <c r="AC34" s="9"/>
@@ -4624,7 +4619,7 @@
         <v>128978.5452912488</v>
       </c>
       <c r="AA36" s="11">
-        <v>134801.66178611427</v>
+        <v>135009.49014608306</v>
       </c>
       <c r="AB36" s="9"/>
       <c r="AC36" s="9"/>
@@ -4773,10 +4768,10 @@
         <v>71833.694064163748</v>
       </c>
       <c r="Z37" s="11">
-        <v>64199.777812919478</v>
+        <v>64343.395330713996</v>
       </c>
       <c r="AA37" s="11">
-        <v>61897.559821004987</v>
+        <v>60786.3051310874</v>
       </c>
       <c r="AB37" s="9"/>
       <c r="AC37" s="9"/>
@@ -4925,10 +4920,10 @@
         <v>309.53287075451669</v>
       </c>
       <c r="Z38" s="11">
-        <v>8054.7954618703516</v>
+        <v>8055.1618497780191</v>
       </c>
       <c r="AA38" s="11">
-        <v>15678.764717622113</v>
+        <v>15681.64194612668</v>
       </c>
       <c r="AB38" s="9"/>
       <c r="AC38" s="9"/>
@@ -5077,10 +5072,10 @@
         <v>122764.24764492556</v>
       </c>
       <c r="Z39" s="11">
-        <v>139518.6736019192</v>
+        <v>139434.17740451708</v>
       </c>
       <c r="AA39" s="11">
-        <v>176888.47606541717</v>
+        <v>178009.59357713506</v>
       </c>
       <c r="AB39" s="9"/>
       <c r="AC39" s="9"/>
@@ -5229,10 +5224,10 @@
         <v>80620.530344301384</v>
       </c>
       <c r="Z40" s="11">
-        <v>93637.33213949982</v>
+        <v>93746.544052597354</v>
       </c>
       <c r="AA40" s="11">
-        <v>85299.312527043716</v>
+        <v>85414.086090693745</v>
       </c>
       <c r="AB40" s="9"/>
       <c r="AC40" s="9"/>
@@ -5381,10 +5376,10 @@
         <v>8419.3043583023664</v>
       </c>
       <c r="Z41" s="11">
-        <v>5911.5959733079471</v>
+        <v>5912.37733664199</v>
       </c>
       <c r="AA41" s="11">
-        <v>5732.0672547734075</v>
+        <v>5737.4855192477244</v>
       </c>
       <c r="AB41" s="9"/>
       <c r="AC41" s="9"/>
@@ -5533,10 +5528,10 @@
         <v>42250.673371536352</v>
       </c>
       <c r="Z42" s="11">
-        <v>47073.824185868027</v>
+        <v>47410.848849754708</v>
       </c>
       <c r="AA42" s="11">
-        <v>48689.822448389219</v>
+        <v>49225.705690305673</v>
       </c>
       <c r="AB42" s="9"/>
       <c r="AC42" s="9"/>
@@ -5685,10 +5680,10 @@
         <v>400079.74064559257</v>
       </c>
       <c r="Z43" s="11">
-        <v>457730.71181424888</v>
+        <v>458367.99343509716</v>
       </c>
       <c r="AA43" s="11">
-        <v>507979.62194146274</v>
+        <v>505687.42643444787</v>
       </c>
       <c r="AB43" s="9"/>
       <c r="AC43" s="9"/>
@@ -5934,10 +5929,10 @@
         <v>3311159.9508674257</v>
       </c>
       <c r="Z45" s="8">
-        <v>3340545.3092117803</v>
+        <v>3342152.8430307843</v>
       </c>
       <c r="AA45" s="8">
-        <v>3876523.2874450604</v>
+        <v>3879440.4460922973</v>
       </c>
       <c r="AB45" s="9"/>
       <c r="AC45" s="9"/>
@@ -6249,7 +6244,7 @@
     </row>
     <row r="52" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:96" x14ac:dyDescent="0.2">
@@ -6259,7 +6254,7 @@
     </row>
     <row r="55" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:96" x14ac:dyDescent="0.2">
@@ -6461,10 +6456,10 @@
         <v>1948771.4521090775</v>
       </c>
       <c r="Z61" s="8">
-        <v>1862281.1161314137</v>
+        <v>1862329.0523636155</v>
       </c>
       <c r="AA61" s="8">
-        <v>2221590.5680856272</v>
+        <v>2235165.3404446486</v>
       </c>
       <c r="AB61" s="9"/>
       <c r="AC61" s="9"/>
@@ -6613,10 +6608,10 @@
         <v>1480398.1772792635</v>
       </c>
       <c r="Z62" s="11">
-        <v>1288737.0795779584</v>
+        <v>1288739.7200753433</v>
       </c>
       <c r="AA62" s="11">
-        <v>1590761.6006561832</v>
+        <v>1603282.5358396347</v>
       </c>
       <c r="AB62" s="9"/>
       <c r="AC62" s="9"/>
@@ -6765,10 +6760,10 @@
         <v>139163.5032120829</v>
       </c>
       <c r="Z63" s="11">
-        <v>177347.68955712512</v>
+        <v>177358.51720745181</v>
       </c>
       <c r="AA63" s="11">
-        <v>199544.57921212009</v>
+        <v>193169.67777299692</v>
       </c>
       <c r="AB63" s="9"/>
       <c r="AC63" s="9"/>
@@ -6920,7 +6915,7 @@
         <v>46398.055407923304</v>
       </c>
       <c r="AA64" s="11">
-        <v>54458.201633477431</v>
+        <v>54834.371022223837</v>
       </c>
       <c r="AB64" s="9"/>
       <c r="AC64" s="9"/>
@@ -7069,10 +7064,10 @@
         <v>55401.84663627694</v>
       </c>
       <c r="Z65" s="11">
-        <v>99347.587919818383</v>
+        <v>99351.751410772849</v>
       </c>
       <c r="AA65" s="11">
-        <v>105352.45694726531</v>
+        <v>106750.73437268363</v>
       </c>
       <c r="AB65" s="9"/>
       <c r="AC65" s="9"/>
@@ -7221,10 +7216,10 @@
         <v>40851.901412739455</v>
       </c>
       <c r="Z66" s="11">
-        <v>47006.352723598495</v>
+        <v>47033.92762418255</v>
       </c>
       <c r="AA66" s="11">
-        <v>54274.061623703259</v>
+        <v>53188.786500203365</v>
       </c>
       <c r="AB66" s="9"/>
       <c r="AC66" s="9"/>
@@ -7373,10 +7368,10 @@
         <v>30922.952196088649</v>
       </c>
       <c r="Z67" s="11">
-        <v>28777.12743662229</v>
+        <v>28777.666973740488</v>
       </c>
       <c r="AA67" s="11">
-        <v>14465.647666423276</v>
+        <v>24082.554028161205</v>
       </c>
       <c r="AB67" s="9"/>
       <c r="AC67" s="9"/>
@@ -7528,7 +7523,7 @@
         <v>161685.45411814674</v>
       </c>
       <c r="AA68" s="11">
-        <v>185017.35825530009</v>
+        <v>182110.51336657978</v>
       </c>
       <c r="AB68" s="9"/>
       <c r="AC68" s="9"/>
@@ -7677,10 +7672,10 @@
         <v>7861.0649967040572</v>
       </c>
       <c r="Z69" s="11">
-        <v>9540.3030889059628</v>
+        <v>9542.4932447394622</v>
       </c>
       <c r="AA69" s="11">
-        <v>13547.942277613569</v>
+        <v>13581.38128533843</v>
       </c>
       <c r="AB69" s="9"/>
       <c r="AC69" s="9"/>
@@ -7832,7 +7827,7 @@
         <v>3441.466301314812</v>
       </c>
       <c r="AA70" s="11">
-        <v>4168.7198135411318</v>
+        <v>4164.786256826319</v>
       </c>
       <c r="AB70" s="9"/>
       <c r="AC70" s="9"/>
@@ -7981,10 +7976,10 @@
         <v>182865.39149853282</v>
       </c>
       <c r="Z71" s="8">
-        <v>194822.89938174962</v>
+        <v>195321.36834938967</v>
       </c>
       <c r="AA71" s="8">
-        <v>209764.05039854132</v>
+        <v>211061.38906129365</v>
       </c>
       <c r="AB71" s="9"/>
       <c r="AC71" s="9"/>
@@ -8133,10 +8128,10 @@
         <v>42754.634304551932</v>
       </c>
       <c r="Z72" s="11">
-        <v>47316.457601565358</v>
+        <v>47292.146080405233</v>
       </c>
       <c r="AA72" s="11">
-        <v>66546.761659581709</v>
+        <v>66717.856912492396</v>
       </c>
       <c r="AB72" s="9"/>
       <c r="AC72" s="9"/>
@@ -8285,10 +8280,10 @@
         <v>53655.570970186411</v>
       </c>
       <c r="Z73" s="11">
-        <v>74946.469904900703</v>
+        <v>76062.230039630202</v>
       </c>
       <c r="AA73" s="11">
-        <v>66724.051793880091</v>
+        <v>67680.541977698187</v>
       </c>
       <c r="AB73" s="9"/>
       <c r="AC73" s="9"/>
@@ -8437,10 +8432,10 @@
         <v>3171.3421047910588</v>
       </c>
       <c r="Z74" s="11">
-        <v>1905.5273571369044</v>
+        <v>2082.0433828784617</v>
       </c>
       <c r="AA74" s="11">
-        <v>1112.2852657017052</v>
+        <v>1321.600451759974</v>
       </c>
       <c r="AB74" s="9"/>
       <c r="AC74" s="9"/>
@@ -8589,10 +8584,10 @@
         <v>13025.784360251646</v>
       </c>
       <c r="Z75" s="11">
-        <v>11817.949326277958</v>
+        <v>11828.061690711573</v>
       </c>
       <c r="AA75" s="11">
-        <v>17122.620734880893</v>
+        <v>17191.805419108106</v>
       </c>
       <c r="AB75" s="9"/>
       <c r="AC75" s="9"/>
@@ -8741,10 +8736,10 @@
         <v>4078.2168226175045</v>
       </c>
       <c r="Z76" s="11">
-        <v>3696.7153388926031</v>
+        <v>3586.3918573378387</v>
       </c>
       <c r="AA76" s="11">
-        <v>2841.4761356442946</v>
+        <v>2788.0528587675426</v>
       </c>
       <c r="AB76" s="9"/>
       <c r="AC76" s="9"/>
@@ -8893,10 +8888,10 @@
         <v>26337.727113641125</v>
       </c>
       <c r="Z77" s="11">
-        <v>18845.996352419214</v>
+        <v>18845.862772699467</v>
       </c>
       <c r="AA77" s="11">
-        <v>20771.965202935819</v>
+        <v>20782.831066361745</v>
       </c>
       <c r="AB77" s="9"/>
       <c r="AC77" s="9"/>
@@ -9045,7 +9040,7 @@
         <v>5.5648529281942589E-2</v>
       </c>
       <c r="Z78" s="11">
-        <v>0.45194088671231664</v>
+        <v>0</v>
       </c>
       <c r="AA78" s="11">
         <v>0</v>
@@ -9197,10 +9192,10 @@
         <v>39842.060173963866</v>
       </c>
       <c r="Z79" s="11">
-        <v>36293.331559670201</v>
+        <v>35624.632525726891</v>
       </c>
       <c r="AA79" s="11">
-        <v>34644.889605916818</v>
+        <v>34578.70037510572</v>
       </c>
       <c r="AB79" s="9"/>
       <c r="AC79" s="9"/>
@@ -9349,10 +9344,10 @@
         <v>22801.514944732415</v>
       </c>
       <c r="Z80" s="8">
-        <v>26952.400050802284</v>
+        <v>26818.493845809833</v>
       </c>
       <c r="AA80" s="8">
-        <v>24067.340714193233</v>
+        <v>23989.187403360404</v>
       </c>
       <c r="AB80" s="9"/>
       <c r="AC80" s="9"/>
@@ -9501,10 +9496,10 @@
         <v>9947.4801600731662</v>
       </c>
       <c r="Z81" s="11">
-        <v>10845.845541125755</v>
+        <v>10682.279696434527</v>
       </c>
       <c r="AA81" s="11">
-        <v>10330.078870694662</v>
+        <v>10326.803774247137</v>
       </c>
       <c r="AB81" s="9"/>
       <c r="AC81" s="9"/>
@@ -9653,10 +9648,10 @@
         <v>12854.034784659249</v>
       </c>
       <c r="Z82" s="11">
-        <v>16106.554509676529</v>
+        <v>16136.214149375304</v>
       </c>
       <c r="AA82" s="11">
-        <v>13737.261843498572</v>
+        <v>13662.383629113268</v>
       </c>
       <c r="AB82" s="9"/>
       <c r="AC82" s="9"/>
@@ -9805,10 +9800,10 @@
         <v>37209.232708686162</v>
       </c>
       <c r="Z83" s="11">
-        <v>34932.677959477958</v>
+        <v>34987.785406724477</v>
       </c>
       <c r="AA83" s="11">
-        <v>37121.227678142808</v>
+        <v>37195.010711175928</v>
       </c>
       <c r="AB83" s="9"/>
       <c r="AC83" s="9"/>
@@ -10112,7 +10107,7 @@
         <v>124867.22053043259</v>
       </c>
       <c r="AA85" s="11">
-        <v>129156.56475490249</v>
+        <v>129312.26492545867</v>
       </c>
       <c r="AB85" s="9"/>
       <c r="AC85" s="9"/>
@@ -10261,10 +10256,10 @@
         <v>66174.334408616996</v>
       </c>
       <c r="Z86" s="11">
-        <v>58273.70621859227</v>
+        <v>58390.299019844955</v>
       </c>
       <c r="AA86" s="11">
-        <v>53706.943171578678</v>
+        <v>52790.734964598523</v>
       </c>
       <c r="AB86" s="9"/>
       <c r="AC86" s="9"/>
@@ -10413,10 +10408,10 @@
         <v>285.57177181990301</v>
       </c>
       <c r="Z87" s="11">
-        <v>6153.853535497281</v>
+        <v>6154.202302628215</v>
       </c>
       <c r="AA87" s="11">
-        <v>14967.885953209419</v>
+        <v>14993.425526225199</v>
       </c>
       <c r="AB87" s="9"/>
       <c r="AC87" s="9"/>
@@ -10565,10 +10560,10 @@
         <v>114143.75193533023</v>
       </c>
       <c r="Z88" s="11">
-        <v>127802.6701260751</v>
+        <v>127732.93318493277</v>
       </c>
       <c r="AA88" s="11">
-        <v>163542.18003766847</v>
+        <v>165122.94174908262</v>
       </c>
       <c r="AB88" s="9"/>
       <c r="AC88" s="9"/>
@@ -10717,10 +10712,10 @@
         <v>75348.676569238829</v>
       </c>
       <c r="Z89" s="11">
-        <v>88355.374707452473</v>
+        <v>88456.136739931331</v>
       </c>
       <c r="AA89" s="11">
-        <v>79862.068963864687</v>
+        <v>79989.699760902746</v>
       </c>
       <c r="AB89" s="9"/>
       <c r="AC89" s="9"/>
@@ -10869,10 +10864,10 @@
         <v>8471.8934967273508</v>
       </c>
       <c r="Z90" s="11">
-        <v>5909.4900662630444</v>
+        <v>5910.4003004899769</v>
       </c>
       <c r="AA90" s="11">
-        <v>5650.1698074464357</v>
+        <v>5662.9251917165275</v>
       </c>
       <c r="AB90" s="9"/>
       <c r="AC90" s="9"/>
@@ -11021,10 +11016,10 @@
         <v>37060.316989501516</v>
       </c>
       <c r="Z91" s="11">
-        <v>38170.836507855798</v>
+        <v>38457.059711147755</v>
       </c>
       <c r="AA91" s="11">
-        <v>38237.167602540037</v>
+        <v>38639.35113243341</v>
       </c>
       <c r="AB91" s="9"/>
       <c r="AC91" s="9"/>
@@ -11173,10 +11168,10 @@
         <v>404836.89335413231</v>
       </c>
       <c r="Z92" s="11">
-        <v>456865.49673516653</v>
+        <v>457579.92721665365</v>
       </c>
       <c r="AA92" s="11">
-        <v>525556.88994866714</v>
+        <v>534983.97129878786</v>
       </c>
       <c r="AB92" s="9"/>
       <c r="AC92" s="9"/>
@@ -11422,10 +11417,10 @@
         <v>3093829.7218533223</v>
       </c>
       <c r="Z94" s="8">
-        <v>3072373.5115250731</v>
+        <v>3073990.6485458957</v>
       </c>
       <c r="AA94" s="8">
-        <v>3506891.1444042278</v>
+        <v>3532574.3294575294</v>
       </c>
       <c r="AB94" s="9"/>
       <c r="AC94" s="9"/>
@@ -11737,7 +11732,7 @@
     </row>
     <row r="101" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103" spans="1:96" x14ac:dyDescent="0.2">
@@ -11747,7 +11742,7 @@
     </row>
     <row r="104" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="105" spans="1:96" x14ac:dyDescent="0.2">
@@ -11863,7 +11858,7 @@
         <v>78</v>
       </c>
       <c r="Z108" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA108" s="17"/>
     </row>
@@ -11944,10 +11939,10 @@
         <v>-9.2516763457003464</v>
       </c>
       <c r="Y110" s="18">
-        <v>-4.7535168620125745</v>
+        <v>-4.7510239564269625</v>
       </c>
       <c r="Z110" s="18">
-        <v>22.514962525890624</v>
+        <v>22.586513547888941</v>
       </c>
       <c r="AA110" s="18"/>
       <c r="AB110" s="9"/>
@@ -12089,10 +12084,10 @@
         <v>-6.9514796053766048</v>
       </c>
       <c r="Y111" s="18">
-        <v>-14.414516128143504</v>
+        <v>-14.414349757542269</v>
       </c>
       <c r="Z111" s="18">
-        <v>27.468573167724642</v>
+        <v>27.580666683625694</v>
       </c>
       <c r="AA111" s="18"/>
       <c r="AB111" s="9"/>
@@ -12234,10 +12229,10 @@
         <v>-29.103836418173174</v>
       </c>
       <c r="Y112" s="18">
-        <v>28.557422007844139</v>
+        <v>28.565662473453784</v>
       </c>
       <c r="Z112" s="18">
-        <v>16.403823009126882</v>
+        <v>12.319461661815097</v>
       </c>
       <c r="AA112" s="18"/>
       <c r="AB112" s="9"/>
@@ -12382,7 +12377,7 @@
         <v>0.17276501617192253</v>
       </c>
       <c r="Z113" s="18">
-        <v>20.506830175050624</v>
+        <v>21.516753522901737</v>
       </c>
       <c r="AA113" s="18"/>
       <c r="AB113" s="9"/>
@@ -12524,10 +12519,10 @@
         <v>3.7980426100805715</v>
       </c>
       <c r="Y114" s="18">
-        <v>83.007940648514193</v>
+        <v>83.01509748901114</v>
       </c>
       <c r="Z114" s="18">
-        <v>6.9116438432236293</v>
+        <v>7.8287110268641129</v>
       </c>
       <c r="AA114" s="18"/>
       <c r="AB114" s="9"/>
@@ -12669,10 +12664,10 @@
         <v>-15.076478900390867</v>
       </c>
       <c r="Y115" s="18">
-        <v>13.42824141104802</v>
+        <v>13.490728023456214</v>
       </c>
       <c r="Z115" s="18">
-        <v>16.977315886969976</v>
+        <v>14.383776358332796</v>
       </c>
       <c r="AA115" s="18"/>
       <c r="AB115" s="9"/>
@@ -12814,10 +12809,10 @@
         <v>21.460986059486459</v>
       </c>
       <c r="Y116" s="18">
-        <v>-4.6629501194135798</v>
+        <v>-4.6613717247466866</v>
       </c>
       <c r="Z116" s="18">
-        <v>-48.633007783441549</v>
+        <v>-15.506827327530303</v>
       </c>
       <c r="AA116" s="18"/>
       <c r="AB116" s="9"/>
@@ -12962,7 +12957,7 @@
         <v>14.450487635677959</v>
       </c>
       <c r="Z117" s="18">
-        <v>15.897568672412987</v>
+        <v>13.827303060768514</v>
       </c>
       <c r="AA117" s="18"/>
       <c r="AB117" s="9"/>
@@ -13104,10 +13099,10 @@
         <v>55.668781728159161</v>
       </c>
       <c r="Y118" s="18">
-        <v>33.246153310002512</v>
+        <v>33.288244231901956</v>
       </c>
       <c r="Z118" s="18">
-        <v>44.660525894017582</v>
+        <v>44.608114460626609</v>
       </c>
       <c r="AA118" s="18"/>
       <c r="AB118" s="9"/>
@@ -13252,7 +13247,7 @@
         <v>90.454009464373087</v>
       </c>
       <c r="Z119" s="18">
-        <v>23.876014660365882</v>
+        <v>23.589148867094067</v>
       </c>
       <c r="AA119" s="18"/>
       <c r="AB119" s="9"/>
@@ -13394,10 +13389,10 @@
         <v>-17.312537329396775</v>
       </c>
       <c r="Y120" s="18">
-        <v>29.636650718502779</v>
+        <v>29.87353566236834</v>
       </c>
       <c r="Z120" s="18">
-        <v>24.060861018412211</v>
+        <v>24.753464949273578</v>
       </c>
       <c r="AA120" s="18"/>
       <c r="AB120" s="9"/>
@@ -13539,10 +13534,10 @@
         <v>12.524286686733262</v>
       </c>
       <c r="Y121" s="18">
-        <v>3.3047507032363512</v>
+        <v>3.2672091454023757</v>
       </c>
       <c r="Z121" s="18">
-        <v>37.211347011460703</v>
+        <v>37.492360347290628</v>
       </c>
       <c r="AA121" s="18"/>
       <c r="AB121" s="9"/>
@@ -13684,10 +13679,10 @@
         <v>-41.827756239750023</v>
       </c>
       <c r="Y122" s="18">
-        <v>92.616219611021705</v>
+        <v>95.484560385252365</v>
       </c>
       <c r="Z122" s="18">
-        <v>26.182981944173164</v>
+        <v>26.302435063818635</v>
       </c>
       <c r="AA122" s="18"/>
       <c r="AB122" s="9"/>
@@ -13829,10 +13824,10 @@
         <v>7.0880977793387387</v>
       </c>
       <c r="Y123" s="18">
-        <v>-16.854236689873375</v>
+        <v>-11.244481148861993</v>
       </c>
       <c r="Z123" s="18">
-        <v>-14.618342086812035</v>
+        <v>-5.0150216062820334</v>
       </c>
       <c r="AA123" s="18"/>
       <c r="AB123" s="9"/>
@@ -13974,10 +13969,10 @@
         <v>-29.532952776680943</v>
       </c>
       <c r="Y124" s="18">
-        <v>26.024096505368306</v>
+        <v>25.913159743898447</v>
       </c>
       <c r="Z124" s="18">
-        <v>77.682494651459677</v>
+        <v>78.320428857135681</v>
       </c>
       <c r="AA124" s="18"/>
       <c r="AB124" s="9"/>
@@ -14119,10 +14114,10 @@
         <v>-11.885897214349811</v>
       </c>
       <c r="Y125" s="18">
-        <v>-28.846230932642058</v>
+        <v>-30.922448634295165</v>
       </c>
       <c r="Z125" s="18">
-        <v>-16.513593571773313</v>
+        <v>-15.723270251024914</v>
       </c>
       <c r="AA125" s="18"/>
       <c r="AB125" s="9"/>
@@ -14264,10 +14259,10 @@
         <v>-1.0826954929252537</v>
       </c>
       <c r="Y126" s="18">
-        <v>10.978440692568398</v>
+        <v>10.973644923369918</v>
       </c>
       <c r="Z126" s="18">
-        <v>15.345470044556933</v>
+        <v>15.391850369237943</v>
       </c>
       <c r="AA126" s="18"/>
       <c r="AB126" s="9"/>
@@ -14554,10 +14549,10 @@
         <v>-11.974101154014079</v>
       </c>
       <c r="Y128" s="18">
-        <v>13.216056062633967</v>
+        <v>10.982641945507311</v>
       </c>
       <c r="Z128" s="18">
-        <v>2.9179814395080541</v>
+        <v>4.7494656013939505</v>
       </c>
       <c r="AA128" s="18"/>
       <c r="AB128" s="9"/>
@@ -14699,10 +14694,10 @@
         <v>1.3392769008106598E-2</v>
       </c>
       <c r="Y129" s="18">
-        <v>16.690002764945987</v>
+        <v>16.08518618547032</v>
       </c>
       <c r="Z129" s="18">
-        <v>-7.8735096312172885</v>
+        <v>-7.3640043742791477</v>
       </c>
       <c r="AA129" s="18"/>
       <c r="AB129" s="9"/>
@@ -14844,10 +14839,10 @@
         <v>-3.1874211772841505</v>
       </c>
       <c r="Y130" s="18">
-        <v>2.3773503972532382</v>
+        <v>0.70198865665854271</v>
       </c>
       <c r="Z130" s="18">
-        <v>-1.138322401904972</v>
+        <v>0.4704254416321163</v>
       </c>
       <c r="AA130" s="18"/>
       <c r="AB130" s="9"/>
@@ -14989,10 +14984,10 @@
         <v>2.7476913607939082</v>
       </c>
       <c r="Y131" s="18">
-        <v>28.210344112524865</v>
+        <v>28.467215874752327</v>
       </c>
       <c r="Z131" s="18">
-        <v>-12.202391326477624</v>
+        <v>-12.307092503679115</v>
       </c>
       <c r="AA131" s="18"/>
       <c r="AB131" s="9"/>
@@ -15134,10 +15129,10 @@
         <v>-15.471714652517647</v>
       </c>
       <c r="Y132" s="18">
-        <v>-4.4767734396496479</v>
+        <v>-4.3297660664391771</v>
       </c>
       <c r="Z132" s="18">
-        <v>5.8656216696128212</v>
+        <v>5.8492200238698473</v>
       </c>
       <c r="AA132" s="18"/>
       <c r="AB132" s="9"/>
@@ -15427,7 +15422,7 @@
         <v>-5.0684907234394103</v>
       </c>
       <c r="Z134" s="18">
-        <v>4.5147946751269217</v>
+        <v>4.6759287300191374</v>
       </c>
       <c r="AA134" s="18"/>
       <c r="AB134" s="9"/>
@@ -15569,10 +15564,10 @@
         <v>-5.1212272477809506</v>
       </c>
       <c r="Y135" s="18">
-        <v>-10.627208235212649</v>
+        <v>-10.42727765992268</v>
       </c>
       <c r="Z135" s="18">
-        <v>-3.5860217439120134</v>
+        <v>-5.5282911032962403</v>
       </c>
       <c r="AA135" s="18"/>
       <c r="AB135" s="9"/>
@@ -15717,7 +15712,7 @@
         <v>64</v>
       </c>
       <c r="Z136" s="18">
-        <v>94.651307930064434</v>
+        <v>94.678173307701172</v>
       </c>
       <c r="AA136" s="18"/>
       <c r="AB136" s="9"/>
@@ -15859,10 +15854,10 @@
         <v>10.816932036760534</v>
       </c>
       <c r="Y137" s="18">
-        <v>13.647642761150564</v>
+        <v>13.578814744017677</v>
       </c>
       <c r="Z137" s="18">
-        <v>26.78480342360703</v>
+        <v>27.665682037701259</v>
       </c>
       <c r="AA137" s="18"/>
       <c r="AB137" s="9"/>
@@ -16004,10 +15999,10 @@
         <v>0.85354195772066532</v>
       </c>
       <c r="Y138" s="18">
-        <v>16.145765525987414</v>
+        <v>16.281229672193248</v>
       </c>
       <c r="Z138" s="18">
-        <v>-8.9045890372380825</v>
+        <v>-8.8882828120347597</v>
       </c>
       <c r="AA138" s="18"/>
       <c r="AB138" s="9"/>
@@ -16149,10 +16144,10 @@
         <v>-33.268908051626624</v>
       </c>
       <c r="Y139" s="18">
-        <v>-29.785220705574574</v>
+        <v>-29.775940089257716</v>
       </c>
       <c r="Z139" s="18">
-        <v>-3.0368908725350678</v>
+        <v>-2.9580625091428487</v>
       </c>
       <c r="AA139" s="18"/>
       <c r="AB139" s="9"/>
@@ -16294,10 +16289,10 @@
         <v>-3.100304612201171</v>
       </c>
       <c r="Y140" s="18">
-        <v>11.415559633615118</v>
+        <v>12.21323843253748</v>
       </c>
       <c r="Z140" s="18">
-        <v>3.4329020224499516</v>
+        <v>3.8279357669850071</v>
       </c>
       <c r="AA140" s="18"/>
       <c r="AB140" s="9"/>
@@ -16439,10 +16434,10 @@
         <v>-5.2176893458169218</v>
       </c>
       <c r="Y141" s="18">
-        <v>14.409870161290158</v>
+        <v>14.569158812052606</v>
       </c>
       <c r="Z141" s="18">
-        <v>10.977832343398731</v>
+        <v>10.32345924608083</v>
       </c>
       <c r="AA141" s="18"/>
       <c r="AB141" s="9"/>
@@ -16676,10 +16671,10 @@
         <v>-7.2893372873518558</v>
       </c>
       <c r="Y143" s="18">
-        <v>0.88746417510445497</v>
+        <v>0.93601313809197961</v>
       </c>
       <c r="Z143" s="18">
-        <v>16.044625311780209</v>
+        <v>16.076093114110293</v>
       </c>
       <c r="AA143" s="18"/>
       <c r="AB143" s="9"/>
@@ -16981,7 +16976,7 @@
     </row>
     <row r="150" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152" spans="1:92" x14ac:dyDescent="0.2">
@@ -16991,7 +16986,7 @@
     </row>
     <row r="153" spans="1:92" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="154" spans="1:92" x14ac:dyDescent="0.2">
@@ -17107,7 +17102,7 @@
         <v>78</v>
       </c>
       <c r="Z157" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AA157" s="17"/>
     </row>
@@ -17188,10 +17183,10 @@
         <v>-9.6721190167930331</v>
       </c>
       <c r="Y159" s="18">
-        <v>-4.4381980187599055</v>
+        <v>-4.4357382006960648</v>
       </c>
       <c r="Z159" s="18">
-        <v>19.294050121746409</v>
+        <v>20.019893241091836</v>
       </c>
       <c r="AA159" s="18"/>
       <c r="AB159" s="9"/>
@@ -17333,10 +17328,10 @@
         <v>-6.9797335749590275</v>
       </c>
       <c r="Y160" s="18">
-        <v>-12.946591034957081</v>
+        <v>-12.946412670958424</v>
       </c>
       <c r="Z160" s="18">
-        <v>23.435697308960272</v>
+        <v>24.407008712814601</v>
       </c>
       <c r="AA160" s="18"/>
       <c r="AB160" s="9"/>
@@ -17478,10 +17473,10 @@
         <v>-30.842432022015103</v>
       </c>
       <c r="Y161" s="18">
-        <v>27.438362403718841</v>
+        <v>27.446142928121262</v>
       </c>
       <c r="Z161" s="18">
-        <v>12.51602978895599</v>
+        <v>8.9148019584823146</v>
       </c>
       <c r="AA161" s="18"/>
       <c r="AB161" s="9"/>
@@ -17626,7 +17621,7 @@
         <v>-0.66264794896936507</v>
       </c>
       <c r="Z162" s="18">
-        <v>17.37173283382414</v>
+        <v>18.182476701081484</v>
       </c>
       <c r="AA162" s="18"/>
       <c r="AB162" s="9"/>
@@ -17768,10 +17763,10 @@
         <v>3.2783550133479196</v>
       </c>
       <c r="Y163" s="18">
-        <v>79.321798733629066</v>
+        <v>79.329313809763278</v>
       </c>
       <c r="Z163" s="18">
-        <v>6.0443027890051439</v>
+        <v>7.4472597179685778</v>
       </c>
       <c r="AA163" s="18"/>
       <c r="AB163" s="9"/>
@@ -17913,10 +17908,10 @@
         <v>-16.068386862936691</v>
       </c>
       <c r="Y164" s="18">
-        <v>15.065275049694037</v>
+        <v>15.132774724447117</v>
       </c>
       <c r="Z164" s="18">
-        <v>15.461120633714216</v>
+        <v>13.085998101626302</v>
       </c>
       <c r="AA164" s="18"/>
       <c r="AB164" s="9"/>
@@ -18058,10 +18053,10 @@
         <v>22.577073793378304</v>
       </c>
       <c r="Y165" s="18">
-        <v>-6.9392622860173674</v>
+        <v>-6.9375175072046034</v>
       </c>
       <c r="Z165" s="18">
-        <v>-49.732134667430238</v>
+        <v>-16.315127108335631</v>
       </c>
       <c r="AA165" s="18"/>
       <c r="AB165" s="9"/>
@@ -18206,7 +18201,7 @@
         <v>11.067234631086677</v>
       </c>
       <c r="Z166" s="18">
-        <v>14.430428676722059</v>
+        <v>12.632589220739703</v>
       </c>
       <c r="AA166" s="18"/>
       <c r="AB166" s="9"/>
@@ -18348,10 +18343,10 @@
         <v>56.110545614080308</v>
       </c>
       <c r="Y167" s="18">
-        <v>21.361457931030543</v>
+        <v>21.38931873404411</v>
       </c>
       <c r="Z167" s="18">
-        <v>42.007461936591199</v>
+        <v>42.325291064004745</v>
       </c>
       <c r="AA167" s="18"/>
       <c r="AB167" s="9"/>
@@ -18496,7 +18491,7 @@
         <v>82.083353690944449</v>
       </c>
       <c r="Z168" s="18">
-        <v>21.132082913276619</v>
+        <v>21.017784054289962</v>
       </c>
       <c r="AA168" s="18"/>
       <c r="AB168" s="9"/>
@@ -18638,10 +18633,10 @@
         <v>-14.258866647455804</v>
       </c>
       <c r="Y169" s="18">
-        <v>6.5389671524109758</v>
+        <v>6.8115550727141141</v>
       </c>
       <c r="Z169" s="18">
-        <v>7.6690938612482995</v>
+        <v>8.0585246995343169</v>
       </c>
       <c r="AA169" s="18"/>
       <c r="AB169" s="9"/>
@@ -18783,10 +18778,10 @@
         <v>4.6903182905740977</v>
       </c>
       <c r="Y170" s="18">
-        <v>10.669775034253419</v>
+        <v>10.612912143117569</v>
       </c>
       <c r="Z170" s="18">
-        <v>40.641892975056862</v>
+        <v>41.07597654599968</v>
       </c>
       <c r="AA170" s="18"/>
       <c r="AB170" s="9"/>
@@ -18928,10 +18923,10 @@
         <v>-25.710291475240879</v>
       </c>
       <c r="Y171" s="18">
-        <v>39.680686552649917</v>
+        <v>41.760172642453085</v>
       </c>
       <c r="Z171" s="18">
-        <v>-10.971054569286594</v>
+        <v>-11.019513965821091</v>
       </c>
       <c r="AA171" s="18"/>
       <c r="AB171" s="9"/>
@@ -19073,10 +19068,10 @@
         <v>51.110733910106745</v>
       </c>
       <c r="Y172" s="18">
-        <v>-39.91416585873354</v>
+        <v>-34.348193475152215</v>
       </c>
       <c r="Z172" s="18">
-        <v>-41.628480875082396</v>
+        <v>-36.523875408742057</v>
       </c>
       <c r="AA172" s="18"/>
       <c r="AB172" s="9"/>
@@ -19218,10 +19213,10 @@
         <v>-17.739417676447758</v>
       </c>
       <c r="Y173" s="18">
-        <v>-9.2726472400342601</v>
+        <v>-9.195013800435234</v>
       </c>
       <c r="Z173" s="18">
-        <v>44.886564175797076</v>
+        <v>45.347613739693401</v>
       </c>
       <c r="AA173" s="18"/>
       <c r="AB173" s="9"/>
@@ -19363,10 +19358,10 @@
         <v>-18.026481282060587</v>
       </c>
       <c r="Y174" s="18">
-        <v>-9.3546150270657762</v>
+        <v>-12.059804239736323</v>
       </c>
       <c r="Z174" s="18">
-        <v>-23.135111168838492</v>
+        <v>-22.260227836979851</v>
       </c>
       <c r="AA174" s="18"/>
       <c r="AB174" s="9"/>
@@ -19508,10 +19503,10 @@
         <v>-11.607767860774189</v>
       </c>
       <c r="Y175" s="18">
-        <v>-28.44486439128498</v>
+        <v>-28.445371571419273</v>
       </c>
       <c r="Z175" s="18">
-        <v>10.219511956285473</v>
+        <v>10.277949685955548</v>
       </c>
       <c r="AA175" s="18"/>
       <c r="AB175" s="9"/>
@@ -19653,10 +19648,10 @@
         <v>-64.307033050092173</v>
       </c>
       <c r="Y176" s="18">
-        <v>712.13446706302648</v>
-      </c>
-      <c r="Z176" s="18">
         <v>-100</v>
+      </c>
+      <c r="Z176" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="AA176" s="18"/>
       <c r="AB176" s="9"/>
@@ -19798,10 +19793,10 @@
         <v>-16.134586255928596</v>
       </c>
       <c r="Y177" s="18">
-        <v>-8.9069907499730618</v>
+        <v>-10.585365389797275</v>
       </c>
       <c r="Z177" s="18">
-        <v>-4.5419967881514651</v>
+        <v>-2.9359801813136954</v>
       </c>
       <c r="AA177" s="18"/>
       <c r="AB177" s="9"/>
@@ -19943,10 +19938,10 @@
         <v>-6.69333967659027</v>
       </c>
       <c r="Y178" s="18">
-        <v>18.204426838001851</v>
+        <v>17.617157942417407</v>
       </c>
       <c r="Z178" s="18">
-        <v>-10.704276172700887</v>
+        <v>-10.549833479524366</v>
       </c>
       <c r="AA178" s="18"/>
       <c r="AB178" s="9"/>
@@ -20088,10 +20083,10 @@
         <v>-13.162814998054614</v>
       </c>
       <c r="Y179" s="18">
-        <v>9.0310849239832152</v>
+        <v>7.3867906699695851</v>
       </c>
       <c r="Z179" s="18">
-        <v>-4.7554307174612234</v>
+        <v>-3.3277159210317109</v>
       </c>
       <c r="AA179" s="18"/>
       <c r="AB179" s="9"/>
@@ -20233,10 +20228,10 @@
         <v>-0.98460778576455255</v>
       </c>
       <c r="Y180" s="18">
-        <v>25.303492479256604</v>
+        <v>25.53423434510384</v>
       </c>
       <c r="Z180" s="18">
-        <v>-14.710114846440476</v>
+        <v>-15.330922714345647</v>
       </c>
       <c r="AA180" s="18"/>
       <c r="AB180" s="9"/>
@@ -20378,10 +20373,10 @@
         <v>-17.245080792844149</v>
       </c>
       <c r="Y181" s="18">
-        <v>-6.1182523354660958</v>
+        <v>-5.9701507938999043</v>
       </c>
       <c r="Z181" s="18">
-        <v>6.265049937492833</v>
+        <v>6.308559626718278</v>
       </c>
       <c r="AA181" s="18"/>
       <c r="AB181" s="9"/>
@@ -20671,7 +20666,7 @@
         <v>-3.0472694389970769</v>
       </c>
       <c r="Z183" s="18">
-        <v>3.4351242914264333</v>
+        <v>3.5598168807983797</v>
       </c>
       <c r="AA183" s="18"/>
       <c r="AB183" s="9"/>
@@ -20813,10 +20808,10 @@
         <v>0.15719924414965192</v>
       </c>
       <c r="Y184" s="18">
-        <v>-11.939112437821407</v>
+        <v>-11.762922072939546</v>
       </c>
       <c r="Z184" s="18">
-        <v>-7.8367472113118595</v>
+        <v>-9.5898876170223417</v>
       </c>
       <c r="AA184" s="18"/>
       <c r="AB184" s="9"/>
@@ -20961,7 +20956,7 @@
         <v>64</v>
       </c>
       <c r="Z185" s="18">
-        <v>143.22785498338794</v>
+        <v>143.62906496951041</v>
       </c>
       <c r="AA185" s="18"/>
       <c r="AB185" s="9"/>
@@ -21103,10 +21098,10 @@
         <v>-0.81330964960227448</v>
       </c>
       <c r="Y186" s="18">
-        <v>11.966417748808112</v>
+        <v>11.905322034009956</v>
       </c>
       <c r="Z186" s="18">
-        <v>27.964603459643669</v>
+        <v>29.272019072807382</v>
       </c>
       <c r="AA186" s="18"/>
       <c r="AB186" s="9"/>
@@ -21248,10 +21243,10 @@
         <v>16.138133587518894</v>
       </c>
       <c r="Y187" s="18">
-        <v>17.262012725945652</v>
+        <v>17.395740399830245</v>
       </c>
       <c r="Z187" s="18">
-        <v>-9.6126645059334521</v>
+        <v>-9.5713392999748947</v>
       </c>
       <c r="AA187" s="18"/>
       <c r="AB187" s="9"/>
@@ -21393,10 +21388,10 @@
         <v>-35.433144141547487</v>
       </c>
       <c r="Y188" s="18">
-        <v>-30.245935356176872</v>
+        <v>-30.235191191046795</v>
       </c>
       <c r="Z188" s="18">
-        <v>-4.3882002661626274</v>
+        <v>-4.1871124829384883</v>
       </c>
       <c r="AA188" s="18"/>
       <c r="AB188" s="9"/>
@@ -21538,10 +21533,10 @@
         <v>-7.5949130800475331</v>
       </c>
       <c r="Y189" s="18">
-        <v>2.9965192112870227</v>
+        <v>3.768836413465948</v>
       </c>
       <c r="Z189" s="18">
-        <v>0.17377427573688919</v>
+        <v>0.47401289296387006</v>
       </c>
       <c r="AA189" s="18"/>
       <c r="AB189" s="9"/>
@@ -21683,10 +21678,10 @@
         <v>-4.2557426288474858</v>
       </c>
       <c r="Y190" s="18">
-        <v>12.85174455074231</v>
+        <v>13.028218210434744</v>
       </c>
       <c r="Z190" s="18">
-        <v>15.035364610455431</v>
+        <v>16.91596144808274</v>
       </c>
       <c r="AA190" s="18"/>
       <c r="AB190" s="9"/>
@@ -21920,10 +21915,10 @@
         <v>-7.4746697212929263</v>
       </c>
       <c r="Y192" s="18">
-        <v>-0.69351620021919302</v>
+        <v>-0.64124645151906634</v>
       </c>
       <c r="Z192" s="18">
-        <v>14.142734639821427</v>
+        <v>14.918187247204528</v>
       </c>
       <c r="AA192" s="18"/>
       <c r="AB192" s="9"/>
@@ -22022,7 +22017,7 @@
     </row>
     <row r="194" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A194" s="19" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="195" spans="1:96" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -22221,7 +22216,7 @@
     </row>
     <row r="198" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="200" spans="1:96" x14ac:dyDescent="0.2">
@@ -22231,7 +22226,7 @@
     </row>
     <row r="201" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="202" spans="1:96" x14ac:dyDescent="0.2">
@@ -22433,10 +22428,10 @@
         <v>104.76347591102302</v>
       </c>
       <c r="Z207" s="18">
-        <v>104.41779492390771</v>
+        <v>104.41784009430977</v>
       </c>
       <c r="AA207" s="18">
-        <v>107.23705179833327</v>
+        <v>106.6508111588615</v>
       </c>
       <c r="AB207" s="9"/>
       <c r="AC207" s="9"/>
@@ -22585,10 +22580,10 @@
         <v>104.0917816168575</v>
       </c>
       <c r="Z208" s="18">
-        <v>102.33654951226268</v>
+        <v>102.33653876780153</v>
       </c>
       <c r="AA208" s="18">
-        <v>105.68007661985645</v>
+        <v>104.94717280945255</v>
       </c>
       <c r="AB208" s="9"/>
       <c r="AC208" s="9"/>
@@ -22737,10 +22732,10 @@
         <v>102.17898510785513</v>
       </c>
       <c r="Z209" s="18">
-        <v>103.07623749299238</v>
+        <v>103.07655147057353</v>
       </c>
       <c r="AA209" s="18">
-        <v>106.63785531791599</v>
+        <v>106.29870837523508</v>
       </c>
       <c r="AB209" s="9"/>
       <c r="AC209" s="9"/>
@@ -22892,7 +22887,7 @@
         <v>101.34086744005782</v>
       </c>
       <c r="AA210" s="18">
-        <v>104.04776693278943</v>
+        <v>104.19999270837647</v>
       </c>
       <c r="AB210" s="9"/>
       <c r="AC210" s="9"/>
@@ -23038,13 +23033,13 @@
         <v>112.58577809914686</v>
       </c>
       <c r="Y211" s="18">
-        <v>113.15229983004645</v>
+        <v>113.15229983004649</v>
       </c>
       <c r="Z211" s="18">
-        <v>115.4782604110506</v>
+        <v>115.4779369003214</v>
       </c>
       <c r="AA211" s="18">
-        <v>116.42276222293503</v>
+        <v>115.88789812497062</v>
       </c>
       <c r="AB211" s="9"/>
       <c r="AC211" s="9"/>
@@ -23193,10 +23188,10 @@
         <v>107.80100036774955</v>
       </c>
       <c r="Z212" s="18">
-        <v>106.26731556314206</v>
+        <v>106.26352090161977</v>
       </c>
       <c r="AA212" s="18">
-        <v>107.66278096784924</v>
+        <v>107.48300420832646</v>
       </c>
       <c r="AB212" s="9"/>
       <c r="AC212" s="9"/>
@@ -23345,10 +23340,10 @@
         <v>111.83921082243289</v>
       </c>
       <c r="Z213" s="18">
-        <v>114.57485382884136</v>
+        <v>114.57460258512961</v>
       </c>
       <c r="AA213" s="18">
-        <v>117.08007861288962</v>
+        <v>115.68126168557788</v>
       </c>
       <c r="AB213" s="9"/>
       <c r="AC213" s="9"/>
@@ -23500,7 +23495,7 @@
         <v>112.10083138986167</v>
       </c>
       <c r="AA214" s="18">
-        <v>113.53810305950567</v>
+        <v>113.28990478031467</v>
       </c>
       <c r="AB214" s="9"/>
       <c r="AC214" s="9"/>
@@ -23649,10 +23644,10 @@
         <v>122.79814140871804</v>
       </c>
       <c r="Z215" s="18">
-        <v>134.82352845190863</v>
+        <v>134.83516370306884</v>
       </c>
       <c r="AA215" s="18">
-        <v>137.34237808889833</v>
+        <v>136.9978493655228</v>
       </c>
       <c r="AB215" s="9"/>
       <c r="AC215" s="9"/>
@@ -23804,7 +23799,7 @@
         <v>119.66936876193823</v>
       </c>
       <c r="AA216" s="18">
-        <v>122.38016653080932</v>
+        <v>122.21208268129809</v>
       </c>
       <c r="AB216" s="9"/>
       <c r="AC216" s="9"/>
@@ -23953,10 +23948,10 @@
         <v>128.98759575625337</v>
       </c>
       <c r="Z217" s="18">
-        <v>156.95214948115296</v>
+        <v>156.8376671049177</v>
       </c>
       <c r="AA217" s="18">
-        <v>180.84687169760326</v>
+        <v>181.06893889495709</v>
       </c>
       <c r="AB217" s="9"/>
       <c r="AC217" s="9"/>
@@ -24105,10 +24100,10 @@
         <v>147.2253363208082</v>
       </c>
       <c r="Z218" s="18">
-        <v>137.42755563670258</v>
+        <v>137.4482354977857</v>
       </c>
       <c r="AA218" s="18">
-        <v>134.07541399310293</v>
+        <v>133.95677128627813</v>
       </c>
       <c r="AB218" s="9"/>
       <c r="AC218" s="9"/>
@@ -24257,10 +24252,10 @@
         <v>111.475405712056</v>
       </c>
       <c r="Z219" s="18">
-        <v>153.72183340298577</v>
+        <v>153.72244737844602</v>
       </c>
       <c r="AA219" s="18">
-        <v>217.8738525416982</v>
+        <v>218.19974573312203</v>
       </c>
       <c r="AB219" s="9"/>
       <c r="AC219" s="9"/>
@@ -24409,10 +24404,10 @@
         <v>112.2339859671437</v>
       </c>
       <c r="Z220" s="18">
-        <v>155.30749578405553</v>
+        <v>151.73056439010571</v>
       </c>
       <c r="AA220" s="18">
-        <v>227.1726293093426</v>
+        <v>227.0479565831227</v>
       </c>
       <c r="AB220" s="9"/>
       <c r="AC220" s="9"/>
@@ -24561,10 +24556,10 @@
         <v>94.08808384194954</v>
       </c>
       <c r="Z221" s="18">
-        <v>130.69229286865297</v>
+        <v>130.46561016762189</v>
       </c>
       <c r="AA221" s="18">
-        <v>160.2752661071147</v>
+        <v>160.06237018698849</v>
       </c>
       <c r="AB221" s="9"/>
       <c r="AC221" s="9"/>
@@ -24713,10 +24708,10 @@
         <v>126.59924263305152</v>
       </c>
       <c r="Z222" s="18">
-        <v>99.376413670748519</v>
+        <v>99.444464618709688</v>
       </c>
       <c r="AA222" s="18">
-        <v>107.93718415855184</v>
+        <v>107.80651957826524</v>
       </c>
       <c r="AB222" s="9"/>
       <c r="AC222" s="9"/>
@@ -24865,10 +24860,10 @@
         <v>144.0746645758679</v>
       </c>
       <c r="Z223" s="18">
-        <v>223.45260730645927</v>
+        <v>223.444534899014</v>
       </c>
       <c r="AA223" s="18">
-        <v>233.84467563844552</v>
+        <v>233.80629047163603</v>
       </c>
       <c r="AB223" s="9"/>
       <c r="AC223" s="9"/>
@@ -25016,11 +25011,11 @@
       <c r="Y224" s="18">
         <v>177.96829070843967</v>
       </c>
-      <c r="Z224" s="18">
-        <v>135.95826146584866</v>
+      <c r="Z224" s="18" t="s">
+        <v>82</v>
       </c>
       <c r="AA224" s="18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AB224" s="9"/>
       <c r="AC224" s="9"/>
@@ -25169,10 +25164,10 @@
         <v>136.01489217189345</v>
       </c>
       <c r="Z225" s="18">
-        <v>169.0477654022792</v>
+        <v>168.82350571555739</v>
       </c>
       <c r="AA225" s="18">
-        <v>182.25873364908796</v>
+        <v>182.19080600300913</v>
       </c>
       <c r="AB225" s="9"/>
       <c r="AC225" s="9"/>
@@ -25321,10 +25316,10 @@
         <v>145.92147577084816</v>
       </c>
       <c r="Z226" s="18">
-        <v>144.05194345641064</v>
+        <v>144.02083828288553</v>
       </c>
       <c r="AA226" s="18">
-        <v>148.61853863358562</v>
+        <v>149.15023933613463</v>
       </c>
       <c r="AB226" s="9"/>
       <c r="AC226" s="9"/>
@@ -25473,10 +25468,10 @@
         <v>149.16277126421642</v>
       </c>
       <c r="Z227" s="18">
-        <v>140.05995914457728</v>
+        <v>139.87742445910948</v>
       </c>
       <c r="AA227" s="18">
-        <v>145.37902401845452</v>
+        <v>145.37304542847698</v>
       </c>
       <c r="AB227" s="9"/>
       <c r="AC227" s="9"/>
@@ -25625,10 +25620,10 @@
         <v>143.41310208481332</v>
       </c>
       <c r="Z228" s="18">
-        <v>146.7400692888306</v>
+        <v>146.76380543453078</v>
       </c>
       <c r="AA228" s="18">
-        <v>151.05457296548636</v>
+        <v>152.00525653961458</v>
       </c>
       <c r="AB228" s="9"/>
       <c r="AC228" s="9"/>
@@ -25777,10 +25772,10 @@
         <v>101.16684904167637</v>
       </c>
       <c r="Z229" s="18">
-        <v>102.93570456246992</v>
+        <v>102.93174131252904</v>
       </c>
       <c r="AA229" s="18">
-        <v>102.54879061286391</v>
+        <v>102.48699231638977</v>
       </c>
       <c r="AB229" s="9"/>
       <c r="AC229" s="9"/>
@@ -26084,7 +26079,7 @@
         <v>103.29255728072701</v>
       </c>
       <c r="AA231" s="18">
-        <v>104.37073952990647</v>
+        <v>104.40578875013018</v>
       </c>
       <c r="AB231" s="9"/>
       <c r="AC231" s="9"/>
@@ -26233,10 +26228,10 @@
         <v>108.55219732260701</v>
       </c>
       <c r="Z232" s="18">
-        <v>110.1693747984687</v>
+        <v>110.19535164367933</v>
       </c>
       <c r="AA232" s="18">
-        <v>115.25057313960241</v>
+        <v>115.14578300880014</v>
       </c>
       <c r="AB232" s="9"/>
       <c r="AC232" s="9"/>
@@ -26385,10 +26380,10 @@
         <v>108.39056983185469</v>
       </c>
       <c r="Z233" s="18">
-        <v>130.89026925011888</v>
+        <v>130.88880497701513</v>
       </c>
       <c r="AA233" s="18">
-        <v>104.74935984036054</v>
+        <v>104.59012130815411</v>
       </c>
       <c r="AB233" s="9"/>
       <c r="AC233" s="9"/>
@@ -26537,10 +26532,10 @@
         <v>107.55231500930458</v>
       </c>
       <c r="Z234" s="18">
-        <v>109.16726032741451</v>
+        <v>109.16071049792863</v>
       </c>
       <c r="AA234" s="18">
-        <v>108.16076685823477</v>
+        <v>107.80427703839889</v>
       </c>
       <c r="AB234" s="9"/>
       <c r="AC234" s="9"/>
@@ -26689,10 +26684,10 @@
         <v>106.99661097593159</v>
       </c>
       <c r="Z235" s="18">
-        <v>105.9780827703307</v>
+        <v>105.98082564720215</v>
       </c>
       <c r="AA235" s="18">
-        <v>106.8082928901319</v>
+        <v>106.78135603209542</v>
       </c>
       <c r="AB235" s="9"/>
       <c r="AC235" s="9"/>
@@ -26841,10 +26836,10 @@
         <v>99.379251657905058</v>
       </c>
       <c r="Z236" s="18">
-        <v>100.03563601971217</v>
+        <v>100.0334501226905</v>
       </c>
       <c r="AA236" s="18">
-        <v>101.44946877913365</v>
+        <v>101.3166398108218</v>
       </c>
       <c r="AB236" s="9"/>
       <c r="AC236" s="9"/>
@@ -26993,10 +26988,10 @@
         <v>114.00515916662333</v>
       </c>
       <c r="Z237" s="18">
-        <v>123.32405703548031</v>
+        <v>123.28256295686451</v>
       </c>
       <c r="AA237" s="18">
-        <v>127.33637322330023</v>
+        <v>127.39785800643584</v>
       </c>
       <c r="AB237" s="9"/>
       <c r="AC237" s="9"/>
@@ -27145,10 +27140,10 @@
         <v>98.82492115055868</v>
       </c>
       <c r="Z238" s="18">
-        <v>100.1893807007238</v>
+        <v>100.17222482271832</v>
       </c>
       <c r="AA238" s="18">
-        <v>96.655496608764608</v>
+        <v>94.52384623912819</v>
       </c>
       <c r="AB238" s="9"/>
       <c r="AC238" s="9"/>
@@ -27394,10 +27389,10 @@
         <v>107.02463446772741</v>
       </c>
       <c r="Z240" s="18">
-        <v>108.72848944572469</v>
+        <v>108.72358523965381</v>
       </c>
       <c r="AA240" s="18">
-        <v>110.54016585689112</v>
+        <v>109.81907482433735</v>
       </c>
       <c r="AB240" s="9"/>
       <c r="AC240" s="9"/>
@@ -27515,7 +27510,7 @@
     </row>
     <row r="247" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="249" spans="1:96" x14ac:dyDescent="0.2">
@@ -27525,7 +27520,7 @@
     </row>
     <row r="250" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="251" spans="1:96" x14ac:dyDescent="0.2">
@@ -27727,10 +27722,10 @@
         <v>61.658172395336798</v>
       </c>
       <c r="Z256" s="18">
-        <v>58.210642178285163</v>
+        <v>58.18416641183525</v>
       </c>
       <c r="AA256" s="18">
-        <v>61.456311534633969</v>
+        <v>61.447572129303715</v>
       </c>
       <c r="AB256" s="9"/>
       <c r="AC256" s="9"/>
@@ -27879,10 +27874,10 @@
         <v>46.53876166114479</v>
       </c>
       <c r="Z257" s="18">
-        <v>39.480053028718686</v>
+        <v>39.461140324599235</v>
       </c>
       <c r="AA257" s="18">
-        <v>43.366644638956906</v>
+        <v>43.372226404615965</v>
       </c>
       <c r="AB257" s="9"/>
       <c r="AC257" s="9"/>
@@ -28031,10 +28026,10 @@
         <v>4.294442350493898</v>
       </c>
       <c r="Z258" s="18">
-        <v>5.4722600280901608</v>
+        <v>5.4699785396709091</v>
       </c>
       <c r="AA258" s="18">
-        <v>5.4891985394265639</v>
+        <v>5.2929507566518277</v>
       </c>
       <c r="AB258" s="9"/>
       <c r="AC258" s="9"/>
@@ -28183,10 +28178,10 @@
         <v>1.4176028395743385</v>
       </c>
       <c r="Z259" s="18">
-        <v>1.4075603673462163</v>
+        <v>1.4068833483710017</v>
       </c>
       <c r="AA259" s="18">
-        <v>1.4616845691319005</v>
+        <v>1.4728260789360745</v>
       </c>
       <c r="AB259" s="9"/>
       <c r="AC259" s="9"/>
@@ -28332,13 +28327,13 @@
         <v>1.6910170533459927</v>
       </c>
       <c r="Y260" s="18">
-        <v>1.8932478209287371</v>
+        <v>1.8932478209287378</v>
       </c>
       <c r="Z260" s="18">
-        <v>3.434315528479249</v>
+        <v>3.4327979057790712</v>
       </c>
       <c r="AA260" s="18">
-        <v>3.1640269218806543</v>
+        <v>3.1888924193200601</v>
       </c>
       <c r="AB260" s="9"/>
       <c r="AC260" s="9"/>
@@ -28487,10 +28482,10 @@
         <v>1.3300099978753095</v>
       </c>
       <c r="Z261" s="18">
-        <v>1.4953363765419656</v>
+        <v>1.4954405097300207</v>
       </c>
       <c r="AA261" s="18">
-        <v>1.5073549094243972</v>
+        <v>1.4736379234782879</v>
       </c>
       <c r="AB261" s="9"/>
       <c r="AC261" s="9"/>
@@ -28639,10 +28634,10 @@
         <v>1.0444673834027181</v>
       </c>
       <c r="Z262" s="18">
-        <v>0.98700507386409797</v>
+        <v>0.98654666967699667</v>
       </c>
       <c r="AA262" s="18">
-        <v>0.43689642506634974</v>
+        <v>0.71811908786871059</v>
       </c>
       <c r="AB262" s="9"/>
       <c r="AC262" s="9"/>
@@ -28791,10 +28786,10 @@
         <v>4.7827973103806016</v>
       </c>
       <c r="Z263" s="18">
-        <v>5.4257829643293451</v>
+        <v>5.4231732304184845</v>
       </c>
       <c r="AA263" s="18">
-        <v>5.4189071835120384</v>
+        <v>5.3181078574297036</v>
       </c>
       <c r="AB263" s="9"/>
       <c r="AC263" s="9"/>
@@ -28943,10 +28938,10 @@
         <v>0.29153655679952944</v>
       </c>
       <c r="Z264" s="18">
-        <v>0.38504411881497408</v>
+        <v>0.38498048988779376</v>
       </c>
       <c r="AA264" s="18">
-        <v>0.47999366252870568</v>
+        <v>0.47961041118151448</v>
       </c>
       <c r="AB264" s="9"/>
       <c r="AC264" s="9"/>
@@ -29095,10 +29090,10 @@
         <v>6.5306474736889594E-2</v>
       </c>
       <c r="Z265" s="18">
-        <v>0.12328469210046468</v>
+        <v>0.12322539370173038</v>
       </c>
       <c r="AA265" s="18">
-        <v>0.1316046847064577</v>
+        <v>0.13120118982155979</v>
       </c>
       <c r="AB265" s="9"/>
       <c r="AC265" s="9"/>
@@ -29247,10 +29242,10 @@
         <v>7.1235964273615267</v>
       </c>
       <c r="Z266" s="18">
-        <v>9.1535572775484972</v>
+        <v>9.1658727731550442</v>
       </c>
       <c r="AA266" s="18">
-        <v>9.7858749957869868</v>
+        <v>9.8510757646812745</v>
       </c>
       <c r="AB266" s="9"/>
       <c r="AC266" s="9"/>
@@ -29399,10 +29394,10 @@
         <v>1.9010152055964051</v>
       </c>
       <c r="Z267" s="18">
-        <v>1.9465639611710945</v>
+        <v>1.9449206355746995</v>
       </c>
       <c r="AA267" s="18">
-        <v>2.3016202813241105</v>
+        <v>2.3037623140058234</v>
       </c>
       <c r="AB267" s="9"/>
       <c r="AC267" s="9"/>
@@ -29551,10 +29546,10 @@
         <v>1.8063991565996769</v>
       </c>
       <c r="Z268" s="18">
-        <v>3.4488108061559122</v>
+        <v>3.4984851692632808</v>
       </c>
       <c r="AA268" s="18">
-        <v>3.7501196674367958</v>
+        <v>3.8067028623906576</v>
       </c>
       <c r="AB268" s="9"/>
       <c r="AC268" s="9"/>
@@ -29703,10 +29698,10 @@
         <v>0.10749476635608857</v>
       </c>
       <c r="Z269" s="18">
-        <v>8.859112946885056E-2</v>
+        <v>9.4522791866800362E-2</v>
       </c>
       <c r="AA269" s="18">
-        <v>6.5182316631466453E-2</v>
+        <v>7.734792843480473E-2</v>
       </c>
       <c r="AB269" s="9"/>
       <c r="AC269" s="9"/>
@@ -29855,10 +29850,10 @@
         <v>0.37013346053350538</v>
       </c>
       <c r="Z270" s="18">
-        <v>0.46235412230383893</v>
+        <v>0.46172492942589971</v>
       </c>
       <c r="AA270" s="18">
-        <v>0.70793656873475674</v>
+        <v>0.7093190787212017</v>
       </c>
       <c r="AB270" s="9"/>
       <c r="AC270" s="9"/>
@@ -30007,10 +30002,10 @@
         <v>0.15592697685942075</v>
       </c>
       <c r="Z271" s="18">
-        <v>0.10997195928693293</v>
+        <v>0.10671170198261822</v>
       </c>
       <c r="AA271" s="18">
-        <v>7.9117526245356048E-2</v>
+        <v>7.7477739194764916E-2</v>
       </c>
       <c r="AB271" s="9"/>
       <c r="AC271" s="9"/>
@@ -30159,10 +30154,10 @@
         <v>1.1460029886488916</v>
       </c>
       <c r="Z272" s="18">
-        <v>1.260628619711716</v>
+        <v>1.2599678230747173</v>
       </c>
       <c r="AA272" s="18">
-        <v>1.2530334800219989</v>
+        <v>1.2525405930691043</v>
       </c>
       <c r="AB272" s="9"/>
       <c r="AC272" s="9"/>
@@ -30311,7 +30306,7 @@
         <v>2.9909982555060221E-6</v>
       </c>
       <c r="Z273" s="18">
-        <v>1.8393732626018155E-5</v>
+        <v>1.838488547011513E-5</v>
       </c>
       <c r="AA273" s="18">
         <v>0</v>
@@ -30463,10 +30458,10 @@
         <v>1.636620881769284</v>
       </c>
       <c r="Z274" s="18">
-        <v>1.8366182857175264</v>
+        <v>1.7995213370815575</v>
       </c>
       <c r="AA274" s="18">
-        <v>1.6288651553925015</v>
+        <v>1.623925248864919</v>
       </c>
       <c r="AB274" s="9"/>
       <c r="AC274" s="9"/>
@@ -30615,10 +30610,10 @@
         <v>1.00485351354735</v>
       </c>
       <c r="Z275" s="18">
-        <v>1.1622490488083927</v>
+        <v>1.1556688597327451</v>
       </c>
       <c r="AA275" s="18">
-        <v>0.92269612240545273</v>
+        <v>0.92229616420446636</v>
       </c>
       <c r="AB275" s="9"/>
       <c r="AC275" s="9"/>
@@ -30767,10 +30762,10 @@
         <v>0.44811900656856363</v>
       </c>
       <c r="Z276" s="18">
-        <v>0.45473673989379332</v>
+        <v>0.44708002340613973</v>
       </c>
       <c r="AA276" s="18">
-        <v>0.38740300854610366</v>
+        <v>0.38697305321873737</v>
       </c>
       <c r="AB276" s="9"/>
       <c r="AC276" s="9"/>
@@ -30919,10 +30914,10 @@
         <v>0.55673450697878624</v>
       </c>
       <c r="Z277" s="18">
-        <v>0.70751230891459937</v>
+        <v>0.70858883632660552</v>
       </c>
       <c r="AA277" s="18">
-        <v>0.53529311385934908</v>
+        <v>0.53532311098572904</v>
       </c>
       <c r="AB277" s="9"/>
       <c r="AC277" s="9"/>
@@ -31071,10 +31066,10 @@
         <v>1.1368646891884862</v>
       </c>
       <c r="Z278" s="18">
-        <v>1.0764170173345684</v>
+        <v>1.0775550508089289</v>
       </c>
       <c r="AA278" s="18">
-        <v>0.981997713463308</v>
+        <v>0.98261716604107141</v>
       </c>
       <c r="AB278" s="9"/>
       <c r="AC278" s="9"/>
@@ -31223,10 +31218,10 @@
         <v>3.0390343173034688</v>
       </c>
       <c r="Z279" s="18">
-        <v>2.1051890380171914</v>
+        <v>2.1041764683553743</v>
       </c>
       <c r="AA279" s="18">
-        <v>0.10318909878315094</v>
+        <v>0.10311150538379382</v>
       </c>
       <c r="AB279" s="9"/>
       <c r="AC279" s="9"/>
@@ -31375,10 +31370,10 @@
         <v>4.1032400799531539</v>
       </c>
       <c r="Z280" s="18">
-        <v>3.8610027211899123</v>
+        <v>3.8591456270529632</v>
       </c>
       <c r="AA280" s="18">
-        <v>3.4773855795655333</v>
+        <v>3.4801279210788274</v>
       </c>
       <c r="AB280" s="9"/>
       <c r="AC280" s="9"/>
@@ -31527,10 +31522,10 @@
         <v>2.1694419819660316</v>
       </c>
       <c r="Z281" s="18">
-        <v>1.9218352655144129</v>
+        <v>1.9252080426209679</v>
       </c>
       <c r="AA281" s="18">
-        <v>1.5967286981474691</v>
+        <v>1.5668833166988436</v>
       </c>
       <c r="AB281" s="9"/>
       <c r="AC281" s="9"/>
@@ -31679,10 +31674,10 @@
         <v>9.3481702891890887E-3</v>
       </c>
       <c r="Z282" s="18">
-        <v>0.24112217366603911</v>
+        <v>0.24101715954059447</v>
       </c>
       <c r="AA282" s="18">
-        <v>0.40445428945057821</v>
+        <v>0.4042243247198849</v>
       </c>
       <c r="AB282" s="9"/>
       <c r="AC282" s="9"/>
@@ -31831,10 +31826,10 @@
         <v>3.7075903751724515</v>
       </c>
       <c r="Z283" s="18">
-        <v>4.1765239111466919</v>
+        <v>4.1719868585684772</v>
       </c>
       <c r="AA283" s="18">
-        <v>4.5630701262212945</v>
+        <v>4.5885378587636643</v>
       </c>
       <c r="AB283" s="9"/>
       <c r="AC283" s="9"/>
@@ -31983,10 +31978,10 @@
         <v>2.4348123177553291</v>
       </c>
       <c r="Z284" s="18">
-        <v>2.8030552940350342</v>
+        <v>2.8049747709199506</v>
       </c>
       <c r="AA284" s="18">
-        <v>2.200407586955651</v>
+        <v>2.2017114910664524</v>
       </c>
       <c r="AB284" s="9"/>
       <c r="AC284" s="9"/>
@@ -32135,10 +32130,10 @@
         <v>0.25427054214329808</v>
       </c>
       <c r="Z285" s="18">
-        <v>0.1769649990079859</v>
+        <v>0.17690326009388707</v>
       </c>
       <c r="AA285" s="18">
-        <v>0.14786618910140223</v>
+        <v>0.14789466674316418</v>
       </c>
       <c r="AB285" s="9"/>
       <c r="AC285" s="9"/>
@@ -32287,10 +32282,10 @@
         <v>1.2760082266780235</v>
       </c>
       <c r="Z286" s="18">
-        <v>1.40916586450897</v>
+        <v>1.4185721322894631</v>
       </c>
       <c r="AA286" s="18">
-        <v>1.2560177983731322</v>
+        <v>1.2688867473114582</v>
       </c>
       <c r="AB286" s="9"/>
       <c r="AC286" s="9"/>
@@ -32439,10 +32434,10 @@
         <v>12.082766963304916</v>
       </c>
       <c r="Z287" s="18">
-        <v>13.702275210937129</v>
+        <v>13.71475258502638</v>
       </c>
       <c r="AA287" s="18">
-        <v>13.104000267112081</v>
+        <v>13.035060944003387</v>
       </c>
       <c r="AB287" s="9"/>
       <c r="AC287" s="9"/>
@@ -33003,7 +32998,7 @@
     </row>
     <row r="296" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="298" spans="1:96" x14ac:dyDescent="0.2">
@@ -33013,7 +33008,7 @@
     </row>
     <row r="299" spans="1:96" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="300" spans="1:96" x14ac:dyDescent="0.2">
@@ -33215,10 +33210,10 @@
         <v>62.988969248821128</v>
       </c>
       <c r="Z305" s="18">
-        <v>60.613760310900787</v>
+        <v>60.583432589313887</v>
       </c>
       <c r="AA305" s="18">
-        <v>63.349287919315913</v>
+        <v>63.272988251258852</v>
       </c>
       <c r="AB305" s="9"/>
       <c r="AC305" s="9"/>
@@ -33367,10 +33362,10 @@
         <v>47.850021183210053</v>
       </c>
       <c r="Z306" s="18">
-        <v>41.945976774752616</v>
+        <v>41.923996115113816</v>
       </c>
       <c r="AA306" s="18">
-        <v>45.361020207156486</v>
+        <v>45.38567023120045</v>
       </c>
       <c r="AB306" s="9"/>
       <c r="AC306" s="9"/>
@@ -33519,10 +33514,10 @@
         <v>4.498098335183057</v>
       </c>
       <c r="Z307" s="18">
-        <v>5.7723349355753557</v>
+        <v>5.7696505124811797</v>
       </c>
       <c r="AA307" s="18">
-        <v>5.6900705210232561</v>
+        <v>5.4682409981352187</v>
       </c>
       <c r="AB307" s="9"/>
       <c r="AC307" s="9"/>
@@ -33671,10 +33666,10 @@
         <v>1.5097004783534409</v>
       </c>
       <c r="Z308" s="18">
-        <v>1.5101697509718508</v>
+        <v>1.5093752946148744</v>
       </c>
       <c r="AA308" s="18">
-        <v>1.5528911332298887</v>
+        <v>1.5522496034965054</v>
       </c>
       <c r="AB308" s="9"/>
       <c r="AC308" s="9"/>
@@ -33823,10 +33818,10 @@
         <v>1.790720615454205</v>
       </c>
       <c r="Z309" s="18">
-        <v>3.2335778038427354</v>
+        <v>3.2320121552018932</v>
       </c>
       <c r="AA309" s="18">
-        <v>3.0041553218830588</v>
+        <v>3.0218963400856884</v>
       </c>
       <c r="AB309" s="9"/>
       <c r="AC309" s="9"/>
@@ -33975,10 +33970,10 @@
         <v>1.3204314744338161</v>
       </c>
       <c r="Z310" s="18">
-        <v>1.5299686886138186</v>
+        <v>1.5300608557944453</v>
       </c>
       <c r="AA310" s="18">
-        <v>1.5476403283947289</v>
+        <v>1.5056664500070454</v>
       </c>
       <c r="AB310" s="9"/>
       <c r="AC310" s="9"/>
@@ -34127,10 +34122,10 @@
         <v>0.99950401205547335</v>
       </c>
       <c r="Z311" s="18">
-        <v>0.93664156811252497</v>
+        <v>0.93616637992549934</v>
       </c>
       <c r="AA311" s="18">
-        <v>0.41249206407519645</v>
+        <v>0.68172816145270976</v>
       </c>
       <c r="AB311" s="9"/>
       <c r="AC311" s="9"/>
@@ -34279,10 +34274,10 @@
         <v>4.7053137186610634</v>
       </c>
       <c r="Z312" s="18">
-        <v>5.2625585239435582</v>
+        <v>5.2597900450552624</v>
       </c>
       <c r="AA312" s="18">
-        <v>5.2758226770318526</v>
+        <v>5.1551785293798789</v>
       </c>
       <c r="AB312" s="9"/>
       <c r="AC312" s="9"/>
@@ -34431,10 +34426,10 @@
         <v>0.25408848267172823</v>
       </c>
       <c r="Z313" s="18">
-        <v>0.31051898648124726</v>
+        <v>0.31042687944588876</v>
       </c>
       <c r="AA313" s="18">
-        <v>0.38632343348413728</v>
+        <v>0.38446130268472001</v>
       </c>
       <c r="AB313" s="9"/>
       <c r="AC313" s="9"/>
@@ -34583,10 +34578,10 @@
         <v>6.1090948798291363E-2</v>
       </c>
       <c r="Z314" s="18">
-        <v>0.11201327860708341</v>
+        <v>0.11195435168102234</v>
       </c>
       <c r="AA314" s="18">
-        <v>0.11887223303731428</v>
+        <v>0.1178966348166232</v>
       </c>
       <c r="AB314" s="9"/>
       <c r="AC314" s="9"/>
@@ -34735,10 +34730,10 @@
         <v>5.9106482236840581</v>
       </c>
       <c r="Z315" s="18">
-        <v>6.3411202658443342</v>
+        <v>6.3540000826542347</v>
       </c>
       <c r="AA315" s="18">
-        <v>5.9814816531517216</v>
+        <v>5.9747189833003391</v>
       </c>
       <c r="AB315" s="9"/>
       <c r="AC315" s="9"/>
@@ -34887,10 +34882,10 @@
         <v>1.3819323669481158</v>
       </c>
       <c r="Z316" s="18">
-        <v>1.5400620212377201</v>
+        <v>1.5384609612516571</v>
       </c>
       <c r="AA316" s="18">
-        <v>1.8975998660741744</v>
+        <v>1.888646938187363</v>
       </c>
       <c r="AB316" s="9"/>
       <c r="AC316" s="9"/>
@@ -35039,10 +35034,10 @@
         <v>1.7342767958814707</v>
       </c>
       <c r="Z317" s="18">
-        <v>2.4393671415198006</v>
+        <v>2.4743806581067602</v>
       </c>
       <c r="AA317" s="18">
-        <v>1.9026553447587999</v>
+        <v>1.9158985959140844</v>
       </c>
       <c r="AB317" s="9"/>
       <c r="AC317" s="9"/>
@@ -35191,10 +35186,10 @@
         <v>0.10250538620112884</v>
       </c>
       <c r="Z318" s="18">
-        <v>6.2021344409750281E-2</v>
+        <v>6.7730960205208843E-2</v>
       </c>
       <c r="AA318" s="18">
-        <v>3.1717131211116245E-2</v>
+        <v>3.7411822894691138E-2</v>
       </c>
       <c r="AB318" s="9"/>
       <c r="AC318" s="9"/>
@@ -35343,10 +35338,10 @@
         <v>0.42102460482048454</v>
       </c>
       <c r="Z319" s="18">
-        <v>0.38465210307101405</v>
+        <v>0.38477871415473097</v>
       </c>
       <c r="AA319" s="18">
-        <v>0.48825640802117876</v>
+        <v>0.48666507243028412</v>
       </c>
       <c r="AB319" s="9"/>
       <c r="AC319" s="9"/>
@@ -35495,10 +35490,10 @@
         <v>0.13181775305250143</v>
       </c>
       <c r="Z320" s="18">
-        <v>0.12032115642923955</v>
+        <v>0.11666892542546695</v>
       </c>
       <c r="AA320" s="18">
-        <v>8.102550146668501E-2</v>
+        <v>7.8924110259151511E-2</v>
       </c>
       <c r="AB320" s="9"/>
       <c r="AC320" s="9"/>
@@ -35647,10 +35642,10 @@
         <v>0.85129853552068857</v>
       </c>
       <c r="Z321" s="18">
-        <v>0.61340186281792242</v>
+        <v>0.61307482446682826</v>
       </c>
       <c r="AA321" s="18">
-        <v>0.59231850512613182</v>
+        <v>0.58831971044621179</v>
       </c>
       <c r="AB321" s="9"/>
       <c r="AC321" s="9"/>
@@ -35799,7 +35794,7 @@
         <v>1.7986939904568178E-6</v>
       </c>
       <c r="Z322" s="18">
-        <v>1.4709828899936746E-5</v>
+        <v>0</v>
       </c>
       <c r="AA322" s="18">
         <v>0</v>
@@ -35951,10 +35946,10 @@
         <v>1.2877909825656775</v>
       </c>
       <c r="Z323" s="18">
-        <v>1.1812799265299883</v>
+        <v>1.1589050390435827</v>
       </c>
       <c r="AA323" s="18">
-        <v>0.98790889649363511</v>
+        <v>0.97885273316855337</v>
       </c>
       <c r="AB323" s="9"/>
       <c r="AC323" s="9"/>
@@ -36103,10 +36098,10 @@
         <v>0.73699967337159833</v>
       </c>
       <c r="Z324" s="18">
-        <v>0.87725011134546527</v>
+        <v>0.87243251239218678</v>
       </c>
       <c r="AA324" s="18">
-        <v>0.68628707659193511</v>
+        <v>0.67908514205401704</v>
       </c>
       <c r="AB324" s="9"/>
       <c r="AC324" s="9"/>
@@ -36255,10 +36250,10 @@
         <v>0.32152642693322647</v>
       </c>
       <c r="Z325" s="18">
-        <v>0.35301194664128144</v>
+        <v>0.34750527629248373</v>
       </c>
       <c r="AA325" s="18">
-        <v>0.29456514175462384</v>
+        <v>0.29233082763846457</v>
       </c>
       <c r="AB325" s="9"/>
       <c r="AC325" s="9"/>
@@ -36407,10 +36402,10 @@
         <v>0.41547324643837186</v>
       </c>
       <c r="Z326" s="18">
-        <v>0.52423816470418383</v>
+        <v>0.52492723609970293</v>
       </c>
       <c r="AA326" s="18">
-        <v>0.39172193483731138</v>
+        <v>0.38675431441555247</v>
       </c>
       <c r="AB326" s="9"/>
       <c r="AC326" s="9"/>
@@ -36559,10 +36554,10 @@
         <v>1.2026916816351616</v>
       </c>
       <c r="Z327" s="18">
-        <v>1.1369932017848305</v>
+        <v>1.1381877632996351</v>
       </c>
       <c r="AA327" s="18">
-        <v>1.0585223820641056</v>
+        <v>1.0529151616432566</v>
       </c>
       <c r="AB327" s="9"/>
       <c r="AC327" s="9"/>
@@ -36711,10 +36706,10 @@
         <v>2.1678257278951287</v>
       </c>
       <c r="Z328" s="18">
-        <v>1.5292987456779641</v>
+        <v>1.5284942261135657</v>
       </c>
       <c r="AA328" s="18">
-        <v>0.10459655395061475</v>
+        <v>0.1038360964483762</v>
       </c>
       <c r="AB328" s="9"/>
       <c r="AC328" s="9"/>
@@ -36863,10 +36858,10 @@
         <v>4.1628617913132206</v>
       </c>
       <c r="Z329" s="18">
-        <v>4.0641940200965561</v>
+        <v>4.0620559658988924</v>
       </c>
       <c r="AA329" s="18">
-        <v>3.6829362371566967</v>
+        <v>3.6605674181331711</v>
       </c>
       <c r="AB329" s="9"/>
       <c r="AC329" s="9"/>
@@ -37015,10 +37010,10 @@
         <v>2.1389132679537397</v>
       </c>
       <c r="Z330" s="18">
-        <v>1.8966999292239768</v>
+        <v>1.899495011393922</v>
       </c>
       <c r="AA330" s="18">
-        <v>1.5314687841758701</v>
+        <v>1.4943984199960259</v>
       </c>
       <c r="AB330" s="9"/>
       <c r="AC330" s="9"/>
@@ -37167,10 +37162,10 @@
         <v>9.2303648711744412E-3</v>
       </c>
       <c r="Z331" s="18">
-        <v>0.20029639991403958</v>
+        <v>0.20020237555177228</v>
       </c>
       <c r="AA331" s="18">
-        <v>0.4268135318968464</v>
+        <v>0.42443340544026503</v>
       </c>
       <c r="AB331" s="9"/>
       <c r="AC331" s="9"/>
@@ -37319,10 +37314,10 @@
         <v>3.6893999410851142</v>
       </c>
       <c r="Z332" s="18">
-        <v>4.1597374032376706</v>
+        <v>4.1552804737826667</v>
       </c>
       <c r="AA332" s="18">
-        <v>4.663451852465526</v>
+        <v>4.6742949008079124</v>
       </c>
       <c r="AB332" s="9"/>
       <c r="AC332" s="9"/>
@@ -37471,10 +37466,10 @@
         <v>2.4354500196637225</v>
       </c>
       <c r="Z333" s="18">
-        <v>2.8758018638038054</v>
+        <v>2.8775668781482517</v>
       </c>
       <c r="AA333" s="18">
-        <v>2.2772896470224526</v>
+        <v>2.2643458367990279</v>
       </c>
       <c r="AB333" s="9"/>
       <c r="AC333" s="9"/>
@@ -37623,10 +37618,10 @@
         <v>0.27383192542517704</v>
       </c>
       <c r="Z334" s="18">
-        <v>0.192342826941301</v>
+        <v>0.19227125181027474</v>
       </c>
       <c r="AA334" s="18">
-        <v>0.16111620163808424</v>
+        <v>0.1603059033887658</v>
       </c>
       <c r="AB334" s="9"/>
       <c r="AC334" s="9"/>
@@ -37775,10 +37770,10 @@
         <v>1.1978783682801057</v>
       </c>
       <c r="Z335" s="18">
-        <v>1.2423891940439382</v>
+        <v>1.2510467372221603</v>
       </c>
       <c r="AA335" s="18">
-        <v>1.090343726909037</v>
+        <v>1.0938015036294215</v>
       </c>
       <c r="AB335" s="9"/>
       <c r="AC335" s="9"/>
@@ -37927,10 +37922,10 @@
         <v>13.085299766000681</v>
       </c>
       <c r="Z336" s="18">
-        <v>14.870115727185345</v>
+        <v>14.885534132418549</v>
       </c>
       <c r="AA336" s="18">
-        <v>14.9864044336612</v>
+        <v>15.144308977100598</v>
       </c>
       <c r="AB336" s="9"/>
       <c r="AC336" s="9"/>
